--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:10:03+00:00</t>
+    <t>2023-03-24T14:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:10:14+00:00</t>
+    <t>2023-03-24T14:14:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:14:45+00:00</t>
+    <t>2023-03-24T14:36:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:36:11+00:00</t>
+    <t>2023-03-24T14:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:36:59+00:00</t>
+    <t>2023-03-24T14:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:42:38+00:00</t>
+    <t>2023-03-24T15:33:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T15:33:20+00:00</t>
+    <t>2023-03-24T15:33:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T15:33:53+00:00</t>
+    <t>2023-03-24T15:38:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T15:38:14+00:00</t>
+    <t>2023-03-26T08:37:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T08:37:00+00:00</t>
+    <t>2023-03-26T08:42:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T08:42:47+00:00</t>
+    <t>2023-03-26T09:01:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T09:01:05+00:00</t>
+    <t>2023-03-26T09:02:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T09:02:01+00:00</t>
+    <t>2023-03-26T09:07:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T09:07:12+00:00</t>
+    <t>2023-03-26T10:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T10:35:39+00:00</t>
+    <t>2023-03-26T10:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T10:35:51+00:00</t>
+    <t>2023-03-26T10:42:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T10:42:59+00:00</t>
+    <t>2023-03-26T11:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:08:41+00:00</t>
+    <t>2023-03-26T11:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:16:53+00:00</t>
+    <t>2023-03-26T11:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:17:47+00:00</t>
+    <t>2023-03-26T11:23:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:23:31+00:00</t>
+    <t>2023-03-27T11:26:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6122,7 +6122,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T11:26:57+00:00</t>
+    <t>2023-03-27T11:35:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T11:35:12+00:00</t>
+    <t>2023-03-27T12:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T12:01:10+00:00</t>
+    <t>2023-03-27T12:02:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T12:02:15+00:00</t>
+    <t>2023-03-27T12:10:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T12:10:50+00:00</t>
+    <t>2023-03-28T07:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5034,7 +5034,7 @@
         <v>92</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-28T07:37:59+00:00</t>
+    <t>2023-03-28T07:45:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-28T07:45:58+00:00</t>
+    <t>2023-03-28T07:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-28T07:53:05+00:00</t>
+    <t>2023-03-29T10:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-29T10:46:03+00:00</t>
+    <t>2023-03-29T10:52:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-29T10:52:43+00:00</t>
+    <t>2023-03-29T11:10:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-29T11:10:06+00:00</t>
+    <t>2023-03-31T13:54:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-31T13:54:07+00:00</t>
+    <t>2023-03-31T13:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-31T13:55:03+00:00</t>
+    <t>2023-04-01T08:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:28:06+00:00</t>
+    <t>2023-04-01T08:29:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:29:12+00:00</t>
+    <t>2023-04-01T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:49:37+00:00</t>
+    <t>2023-04-01T08:50:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:50:39+00:00</t>
+    <t>2023-04-03T05:56:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T05:56:04+00:00</t>
+    <t>2023-04-03T09:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T09:35:38+00:00</t>
+    <t>2023-04-03T09:37:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T09:37:11+00:00</t>
+    <t>2023-04-03T09:57:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$61</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T09:57:00+00:00</t>
+    <t>2023-04-03T10:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1657,6 +1660,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -2004,7 +2022,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2124,7 +2142,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>91</v>
       </c>
@@ -2244,7 +2262,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>99</v>
       </c>
@@ -2362,7 +2380,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>105</v>
       </c>
@@ -2482,7 +2500,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>111</v>
       </c>
@@ -2602,7 +2620,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>120</v>
       </c>
@@ -2722,7 +2740,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>128</v>
       </c>
@@ -2842,7 +2860,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>136</v>
       </c>
@@ -2962,7 +2980,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>144</v>
       </c>
@@ -3084,7 +3102,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>149</v>
       </c>
@@ -3204,7 +3222,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>158</v>
       </c>
@@ -3324,7 +3342,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>167</v>
       </c>
@@ -3444,7 +3462,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>176</v>
       </c>
@@ -3566,7 +3584,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>190</v>
       </c>
@@ -3688,7 +3706,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>200</v>
       </c>
@@ -3808,7 +3826,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>213</v>
       </c>
@@ -3926,7 +3944,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>219</v>
       </c>
@@ -4046,7 +4064,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>225</v>
       </c>
@@ -4168,7 +4186,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>234</v>
       </c>
@@ -4290,7 +4308,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>243</v>
       </c>
@@ -4412,7 +4430,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>253</v>
       </c>
@@ -4532,7 +4550,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>259</v>
       </c>
@@ -4654,7 +4672,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>270</v>
       </c>
@@ -4774,7 +4792,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>283</v>
       </c>
@@ -4898,7 +4916,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>285</v>
       </c>
@@ -5018,7 +5036,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>293</v>
       </c>
@@ -5138,7 +5156,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>302</v>
       </c>
@@ -5258,7 +5276,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>313</v>
       </c>
@@ -5382,7 +5400,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>315</v>
       </c>
@@ -5504,7 +5522,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>325</v>
       </c>
@@ -5624,7 +5642,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>336</v>
       </c>
@@ -5742,7 +5760,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>337</v>
       </c>
@@ -5862,7 +5880,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>338</v>
       </c>
@@ -5984,7 +6002,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>339</v>
       </c>
@@ -6106,7 +6124,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>341</v>
       </c>
@@ -6125,7 +6143,7 @@
         <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
@@ -6228,7 +6246,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>349</v>
       </c>
@@ -6348,7 +6366,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>360</v>
       </c>
@@ -6470,7 +6488,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>369</v>
       </c>
@@ -6590,7 +6608,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>378</v>
       </c>
@@ -6710,7 +6728,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>387</v>
       </c>
@@ -6832,7 +6850,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>396</v>
       </c>
@@ -6950,7 +6968,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>397</v>
       </c>
@@ -7070,7 +7088,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>398</v>
       </c>
@@ -7192,7 +7210,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>403</v>
       </c>
@@ -7310,7 +7328,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>410</v>
       </c>
@@ -7428,7 +7446,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>414</v>
       </c>
@@ -7550,7 +7568,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>423</v>
       </c>
@@ -7672,7 +7690,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>430</v>
       </c>
@@ -7792,7 +7810,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>436</v>
       </c>
@@ -7910,7 +7928,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>440</v>
       </c>
@@ -8030,7 +8048,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>447</v>
       </c>
@@ -8150,7 +8168,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>453</v>
       </c>
@@ -8272,7 +8290,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>460</v>
       </c>
@@ -8390,7 +8408,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>461</v>
       </c>
@@ -8510,7 +8528,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>462</v>
       </c>
@@ -8632,7 +8650,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>463</v>
       </c>
@@ -8754,7 +8772,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>470</v>
       </c>
@@ -8876,7 +8894,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>475</v>
       </c>
@@ -8998,7 +9016,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>479</v>
       </c>
@@ -9120,7 +9138,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>482</v>
       </c>
@@ -9243,6 +9261,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AP61">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI60">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T10:19:29+00:00</t>
+    <t>2023-04-03T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T10:20:09+00:00</t>
+    <t>2023-04-03T10:41:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T10:41:47+00:00</t>
+    <t>2023-04-04T06:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T06:46:45+00:00</t>
+    <t>2023-04-04T06:47:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T06:47:21+00:00</t>
+    <t>2023-04-04T07:17:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T07:17:27+00:00</t>
+    <t>2023-04-04T08:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T08:23:07+00:00</t>
+    <t>2023-04-04T08:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T08:37:07+00:00</t>
+    <t>2023-04-04T09:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:08:50+00:00</t>
+    <t>2023-04-04T09:09:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:09:26+00:00</t>
+    <t>2023-04-04T09:19:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:19:23+00:00</t>
+    <t>2023-04-04T09:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:25:44+00:00</t>
+    <t>2023-04-04T10:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:05:29+00:00</t>
+    <t>2023-04-04T10:21:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:21:49+00:00</t>
+    <t>2023-04-04T10:30:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:30:43+00:00</t>
+    <t>2023-04-04T10:41:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:41:10+00:00</t>
+    <t>2023-04-04T10:41:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:41:37+00:00</t>
+    <t>2023-04-04T10:49:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:49:31+00:00</t>
+    <t>2023-04-04T13:12:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T13:12:12+00:00</t>
+    <t>2023-04-04T13:39:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T13:39:29+00:00</t>
+    <t>2023-04-17T11:49:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:49:04+00:00</t>
+    <t>2023-04-17T12:05:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:05:39+00:00</t>
+    <t>2023-04-17T12:49:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2378" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2380" uniqueCount="485">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:49:16+00:00</t>
+    <t>2023-05-26T12:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -1680,7 +1680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1767,77 +1767,85 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="B21" t="s" s="2">
         <v>36</v>
       </c>
     </row>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:35:19+00:00</t>
+    <t>2023-05-26T12:35:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:35:50+00:00</t>
+    <t>2023-05-26T12:45:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:45:45+00:00</t>
+    <t>2023-05-26T12:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:47:23+00:00</t>
+    <t>2023-05-26T13:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:04:11+00:00</t>
+    <t>2023-05-26T13:05:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:05:32+00:00</t>
+    <t>2023-05-26T13:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:09:55+00:00</t>
+    <t>2023-05-26T14:47:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:47:38+00:00</t>
+    <t>2023-05-26T14:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:52:17+00:00</t>
+    <t>2023-05-26T14:59:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:59:52+00:00</t>
+    <t>2023-05-26T15:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T15:03:26+00:00</t>
+    <t>2023-05-26T15:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T15:10:57+00:00</t>
+    <t>2023-05-29T05:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-29T05:00:29+00:00</t>
+    <t>2023-05-29T05:09:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-12T13:14:32+00:00</t>
+    <t>2023-06-13T16:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:44:52+00:00</t>
+    <t>2023-06-13T16:48:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:48:27+00:00</t>
+    <t>2023-06-13T16:56:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:56:41+00:00</t>
+    <t>2023-06-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-20T13:48:39+00:00</t>
+    <t>2023-06-20T13:48:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-test-results.xlsx
+++ b/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-20T13:48:52+00:00</t>
+    <t>2023-06-20T13:53:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
